--- a/artfynd/A 52787-2023 artfynd.xlsx
+++ b/artfynd/A 52787-2023 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114922404</v>
+        <v>114922400</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lidbergets ostsluttning, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715674</v>
+        <v>715469</v>
       </c>
       <c r="R2" t="n">
-        <v>7054268</v>
+        <v>7053941</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114922400</v>
+        <v>114922398</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715469</v>
+        <v>715607</v>
       </c>
       <c r="R3" t="n">
-        <v>7053941</v>
+        <v>7054051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,55 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114922396</v>
+        <v>114922401</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lidbergets ostsluttning, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715610</v>
+        <v>715430</v>
       </c>
       <c r="R4" t="n">
-        <v>7054056</v>
+        <v>7053913</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114922398</v>
+        <v>114922396</v>
       </c>
       <c r="B5" t="n">
-        <v>74459</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +977,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lidbergets ostsluttning, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715607</v>
+        <v>715610</v>
       </c>
       <c r="R5" t="n">
-        <v>7054051</v>
+        <v>7054056</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,50 +1068,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114922401</v>
+        <v>114922404</v>
       </c>
       <c r="B6" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lidbergets ostsluttning, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715430</v>
+        <v>715674</v>
       </c>
       <c r="R6" t="n">
-        <v>7053913</v>
+        <v>7054268</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 52787-2023 artfynd.xlsx
+++ b/artfynd/A 52787-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114922400</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114922398</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114922401</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114922396</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,8 +1192,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114922404</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>